--- a/models/sovereigns/Cameroon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Cameroon_Sovereign_Model.xlsx
@@ -702,16 +702,34 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="n">
+        <v>3.3</v>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -788,16 +806,34 @@
           <t>fiscal_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
+      <c r="B10" s="2" t="n">
+        <v>-1.7</v>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -892,16 +928,34 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>-5.1</v>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -909,16 +963,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>1.016</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -926,16 +998,34 @@
           <t>gross_reserves_usd_bn</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
+      <c r="B16" s="2" t="n">
+        <v>5.062</v>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -960,16 +1050,34 @@
           <t>import_cover_months</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
+      <c r="B18" s="2" t="n">
+        <v>5.275</v>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>months</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1046,16 +1154,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>65.13500000000001</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Cameroon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Cameroon_Sovereign_Model.xlsx
@@ -764,22 +764,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>end-Jun-25</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Caisse Autonome d'Amortissement (CAA)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>30-Jun-25</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CAA</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>30-Jun-25</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>total public debt (XAF 14.105 trillion)</t>
+          <t>Total public debt, XAF 14.105 trillion (external ~30% of GDP, domestic 13% of GDP)</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>5.062</v>
+        <v>5.14</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>IMF International Liquidity</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+          <t>Gross official reserves incl. gold at national valuation, end-month (auto-filled; a run's sourced point replaces it unless older)</t>
         </is>
       </c>
     </row>
@@ -1112,22 +1112,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>end-Jun-25</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Caisse Autonome d'Amortissement (CAA)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>30-Jun-25</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>CAA</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>30-Jun-25</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>external public debt</t>
+          <t>External public debt, approximate, as stated by CAA</t>
         </is>
       </c>
     </row>
@@ -1347,20 +1347,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Post-Financing Assessment (PFA); ECF/EFF/RSF completed Jul-25</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>15-Jul-21</t>
+          <t>None active; ECF/EFF/RSF arrangements completed Jul-25, now annual Post-Financing Assessment</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1455,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CAA, 30-Jun-25</t>
+          <t>CAA, end-Jun-25 value shown under 2025, asof 30-Jun-25</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1470,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CAA, 30-Jun-25</t>
+          <t>CAA, approximate, end-Jun-25 value shown under 2025, asof 30-Jun-25</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Cameroon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Cameroon_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/cameroon.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/cameroon.json</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total public debt, XAF 14.105 trillion (external ~30% of GDP, domestic 13% of GDP)</t>
+          <t>total public debt, XAF 14.105 trillion</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-5.1</v>
+        <v>-3.75</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -938,24 +938,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>approx. 3.5%-4.0% deficit, midpoint</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>IMF Cameroon Country Report No. 25/210</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+          <t>Jul-25</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1127,7 +1123,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>External public debt, approximate, as stated by CAA</t>
+          <t>approximate external public debt, % of GDP</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1343,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None active; ECF/EFF/RSF arrangements completed Jul-25, now annual Post-Financing Assessment</t>
+          <t>None; ECF/EFF/RSF completed Jul-25, Post-Financing Assessment</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1455,7 +1451,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CAA, end-Jun-25 value shown under 2025, asof 30-Jun-25</t>
+          <t>CAA, 30-Jun-25 (end-June 2025 reading)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1466,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CAA, approximate, end-Jun-25 value shown under 2025, asof 30-Jun-25</t>
+          <t>CAA, 30-Jun-25 (end-June 2025 reading)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Cameroon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Cameroon_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>approximate external public debt, % of GDP</t>
+          <t>approximate, as stated in source; public external debt</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None; ECF/EFF/RSF completed Jul-25, Post-Financing Assessment</t>
+          <t>ECF/EFF/RSF arrangements completed Jul-25; now Post-Financing Assessment, no active programme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CAA, 30-Jun-25 (end-June 2025 reading)</t>
+          <t>CAA, end-Jun-25 (30-Jun-25)</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CAA, 30-Jun-25 (end-June 2025 reading)</t>
+          <t>CAA, end-Jun-25 (30-Jun-25), approximate</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Cameroon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Cameroon_Sovereign_Model.xlsx
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>end-Jun-25</t>
+          <t>Jun-25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>total public debt, XAF 14.105 trillion</t>
+          <t>Total public debt XAF 14.105 trillion (external ~30% of GDP, domestic 13% of GDP)</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>end-Jun-25</t>
+          <t>Jun-25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>approximate, as stated in source; public external debt</t>
+          <t>Approximate external public debt, per CAA</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ECF/EFF/RSF arrangements completed Jul-25; now Post-Financing Assessment, no active programme</t>
+          <t>None; ECF/EFF/RSF completed Jul-25, now annual Post-Financing Assessment</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">

--- a/models/sovereigns/Cameroon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Cameroon_Sovereign_Model.xlsx
@@ -691,7 +691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>31-Aug-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -764,12 +764,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Jun-25</t>
+          <t>end-Jun-25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Caisse Autonome d'Amortissement (CAA)</t>
+          <t>CAA Debt Statistical Bulletin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total public debt XAF 14.105 trillion (external ~30% of GDP, domestic 13% of GDP)</t>
+          <t>Total public debt, XAF 14.105 trillion</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Jun-25</t>
+          <t>end-Jun-25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Caisse Autonome d'Amortissement (CAA)</t>
+          <t>CAA Debt Statistical Bulletin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Approximate external public debt, per CAA</t>
+          <t>Public external debt, approximate</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None; ECF/EFF/RSF completed Jul-25, now annual Post-Financing Assessment</t>
+          <t>None active; ECF/EFF/RSF completed Jul-25, now Post-Financing Assessment</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CAA, end-Jun-25 (30-Jun-25)</t>
+          <t>CAA, end-Jun-25 reading shown under 2025, asof 30-Jun-25</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CAA, end-Jun-25 (30-Jun-25), approximate</t>
+          <t>CAA, end-Jun-25 reading shown under 2025, approximate, asof 30-Jun-25</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Cameroon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Cameroon_Sovereign_Model.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CAA Debt Statistical Bulletin</t>
+          <t>Caisse Autonome d'Amortissement (CAA)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total public debt, XAF 14.105 trillion</t>
+          <t>total public debt XAF 14.105 trillion (external ~30% of GDP, domestic 13% of GDP)</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CAA Debt Statistical Bulletin</t>
+          <t>Caisse Autonome d'Amortissement (CAA)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Public external debt, approximate</t>
+          <t>approximate, public external debt, share of GDP</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CAA, end-Jun-25 reading shown under 2025, asof 30-Jun-25</t>
+          <t>CAA, end-Jun-25 (30-Jun-25)</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CAA, end-Jun-25 reading shown under 2025, approximate, asof 30-Jun-25</t>
+          <t>CAA, end-Jun-25 (30-Jun-25), approximate</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Cameroon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Cameroon_Sovereign_Model.xlsx
@@ -691,7 +691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31-Aug-26</t>
+          <t>Aug-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -769,7 +769,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Caisse Autonome d'Amortissement (CAA)</t>
+          <t>Caisse Autonome d'Amortissement (CAA), Debt Statistical Bulletin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>total public debt XAF 14.105 trillion (external ~30% of GDP, domestic 13% of GDP)</t>
+          <t>Total public debt XAF 14.105 trillion (external ~30% of GDP, domestic 13% of GDP)</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Caisse Autonome d'Amortissement (CAA)</t>
+          <t>Caisse Autonome d'Amortissement (CAA), Debt Statistical Bulletin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>approximate, public external debt, share of GDP</t>
+          <t>Approximate external public debt, % of GDP (CAA)</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None active; ECF/EFF/RSF completed Jul-25, now Post-Financing Assessment</t>
+          <t>Post-Financing Assessment (ECF/EFF/RSF arrangements completed Jul-25)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CAA, end-Jun-25 (30-Jun-25)</t>
+          <t>CAA, end-Jun-25 reading shown under 2025, asof 30-Jun-25</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CAA, end-Jun-25 (30-Jun-25), approximate</t>
+          <t>CAA, approximate, end-Jun-25 reading shown under 2025, asof 30-Jun-25</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Cameroon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Cameroon_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/cameroon.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/cameroon.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Cameroon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Cameroon_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/cameroon.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/cameroon.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Cameroon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Cameroon_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/cameroon.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/cameroon.json</t>
         </is>
       </c>
     </row>
